--- a/이미지_현황_정리.xlsx
+++ b/이미지_현황_정리.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게임요소_이미지현황" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이미지_전체목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품종별_필요이미지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게임요소_이미지현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이미지_전체목록" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +39,57 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A6B3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00856404"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +141,31 @@
         <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4A7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6F0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD6D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -110,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,6 +243,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,6 +639,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>📸 품종별 포트레이트 이미지 현황 (CAT_PORTRAITS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>✅ 품종 전용  ⚠️ 범용(교체 권장)  ❌ 없음(생성 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>품종</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>챕터1 (아기)</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>챕터2 (청소년)</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>챕터3 (성묘)</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>챕터4 (시니어)</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>필요 생성 이미지</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>생성 프롬프트 키워드</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>코숏 (korean)</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_korean_kitten.jpeg</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_korean_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_korean_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>✅ (adult 재사용)</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>러시안블루 (russian)</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_kitten_sunlight.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_teen_window.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_russian_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_russian_senior.jpeg</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>cat_russian_kitten.jpeg
+cat_russian_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Russian Blue kitten, blue-gray fur, green eyes, watercolor / Russian Blue young cat, teen, blue coat, alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>스코티시폴드 (scottish)</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_kitten_sunlight_v2.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_teen_window_v2.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_scottish_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_scottish_senior.jpeg</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>cat_scottish_kitten.jpeg
+cat_scottish_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Scottish Fold kitten, folded ears, round face, watercolor / Scottish Fold young cat, teen, folded ears</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>페르시안 (persian)</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_kitten_portrait.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_persian_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_persian_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>❌ 없음 (adult 재사용 중)</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>cat_persian_kitten.jpeg
+cat_persian_senior.jpeg</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Persian kitten, long fluffy fur, flat face, watercolor / Persian senior cat, elderly, fluffy, calm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>아비시니안 (abyssinian)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_kitten_sunlight_v3.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_teen_sunlit.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_abyssinian_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_abyssinian_senior.jpeg</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>cat_abyssinian_kitten.jpeg
+cat_abyssinian_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Abyssinian kitten, ticked coat, large ears, curious, watercolor / Abyssinian young cat, slender, active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>메인쿤 (maincoon)</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_kitten_young.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ cat_teen_portrait.jpeg
+(범용, 교체 권장)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_maincoon_adult.jpeg</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>✅ cat_maincoon_senior.jpeg</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>cat_maincoon_kitten.jpeg
+cat_maincoon_teen.jpeg</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Maine Coon kitten, tufted ears, large paws, fluffy, watercolor / Maine Coon young cat, teen, large, shaggy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1"/>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>😸 품종별 무드 이미지 현황 (MOOD_IMGS — 챕터3+ 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>✅ 있음  ❌ 없음 (없으면 코숏 이미지로 fallback 처리됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>품종</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>bored</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>hungry</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>litter</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>필요 생성 이미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>코숏 (korean)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>러시안블루 (russian)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>mood_russian_happy.jpeg
+mood_russian_hungry.jpeg
+mood_russian_litter.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>스코티시폴드 (scottish)</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>mood_scottish_hungry.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>페르시안 (persian)</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>아비시니안 (abyssinian)</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>mood_abyssinian_happy.jpeg
+mood_abyssinian_hungry.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>메인쿤 (maincoon)</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>mood_maincoon_hungry.jpeg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2999,7 +3733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
